--- a/data/syllabus650.xlsx
+++ b/data/syllabus650.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daviddl\Documents\EDLD 650\EDLD 650\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95DBBD5-B0DC-4905-80D9-3E07049DA05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F558228-7336-4B53-8BAB-B622EB599D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14400" yWindow="3900" windowWidth="15735" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15855" yWindow="5550" windowWidth="15285" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,70 +129,70 @@
     <t>Assignments Due</t>
   </si>
   <si>
-    <t>Research project proposal (Jan. 28)</t>
-  </si>
-  <si>
-    <t>Student survey (Jan. 10)</t>
-  </si>
-  <si>
-    <t>Jan. 8</t>
-  </si>
-  <si>
-    <t>Jan. 22</t>
-  </si>
-  <si>
-    <t>Jan. 29</t>
-  </si>
-  <si>
-    <t>Feb. 5</t>
-  </si>
-  <si>
-    <t>Feb. 12</t>
-  </si>
-  <si>
-    <t>Feb. 19</t>
-  </si>
-  <si>
-    <t>Feb. 26</t>
-  </si>
-  <si>
-    <t>Mar. 4</t>
-  </si>
-  <si>
-    <t>Mar. 11</t>
-  </si>
-  <si>
-    <t>DARE #1 (Jan. 21)</t>
-  </si>
-  <si>
-    <t>DARE #3 (Feb. 18)</t>
-  </si>
-  <si>
-    <t>DARE #4 (Mar. 3)</t>
-  </si>
-  <si>
-    <t>Research project presentation (Mar. 11)</t>
-  </si>
-  <si>
-    <t>Final research project (Mar. 20)</t>
-  </si>
-  <si>
     <t>MM Ch. 9 &lt;br&gt; [Angrist &amp; Lavy 1999](https://doi.org/10.1162/003355399556061) &lt;br&gt; [Dee &amp; Penner 2017](https://journals.sagepub.com/doi/full/10.3102/0002831216677002)</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Online</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Common Vocabulary                                    </t>
   </si>
   <si>
     <t>[Liebowitz et al. 2022](https://doi.org/10.1080/19345747.2021.2015496)</t>
   </si>
   <si>
-    <t>DARE #2 (Feb. 4)</t>
+    <t>Apr. 1</t>
+  </si>
+  <si>
+    <t>Apr. 8</t>
+  </si>
+  <si>
+    <t>Apr. 15</t>
+  </si>
+  <si>
+    <t>Apr. 22</t>
+  </si>
+  <si>
+    <t>Apr. 29</t>
+  </si>
+  <si>
+    <t>May 6</t>
+  </si>
+  <si>
+    <t>May 13</t>
+  </si>
+  <si>
+    <t>May 20</t>
+  </si>
+  <si>
+    <t>May 27</t>
+  </si>
+  <si>
+    <t>Jun. 3</t>
+  </si>
+  <si>
+    <t>DARE #1 (Apr. 14)</t>
+  </si>
+  <si>
+    <t>Research project proposal (Apr. 21)</t>
+  </si>
+  <si>
+    <t>DARE #2 (Apr. 28)</t>
+  </si>
+  <si>
+    <t>DARE #3 (May 12)</t>
+  </si>
+  <si>
+    <t>Research project presentation (Jun. 3)</t>
+  </si>
+  <si>
+    <t>Final research project (Jun. 11)</t>
+  </si>
+  <si>
+    <t>DARE #4 (May 26)</t>
+  </si>
+  <si>
+    <t>Course survey (Apr. 3)</t>
   </si>
 </sst>
 </file>
@@ -544,16 +544,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
@@ -578,16 +578,16 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -595,16 +595,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>25</v>
@@ -621,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -629,7 +629,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
@@ -655,7 +655,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -663,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -680,7 +680,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -689,7 +689,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>21</v>
@@ -706,7 +706,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2</v>
@@ -723,7 +723,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
